--- a/site/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mapping and Assignments</t>
+          <t>Basic Details</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,107 +539,107 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01K598XK6ZRCYEKPB5B55JW6FN</t>
+          <t>h_01H0PWCXWT6MJE5NCTTP63J2YS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K598XK6ZRCYEKPB5B55JW6FN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01H0PWCXWT6MJE5NCTTP63J2YS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>User Naming Attributes</t>
+          <t>Source Application</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
+          <t>h_01GYETCNZJJ82ZSS3JSKP4KH0Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETCNZJJ82ZSS3JSKP4KH0Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Preview Values of User Naming Attributes</t>
+          <t>Target Application</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JTR3CGZ78E6XKPZS9QJPKP0J</t>
+          <t>h_01GYETDCC2FX7A96FZVS1MTD7Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JTR3CGZ78E6XKPZS9QJPKP0J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETDCC2FX7A96FZVS1MTD7Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OU Assignment</t>
+          <t>Report Only</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
+          <t>h_01GYETDNX1PS5WSKG76W4CT719</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETDNX1PS5WSKG76W4CT719</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Configure OU Assignment Rules</t>
+          <t>Update Limit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
+          <t>h_01GYETE7WXSJW507TZF27RYGC5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETE7WXSJW507TZF27RYGC5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Using Condition Builder</t>
+          <t>Match Expression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
+          <t>h_01GYETEJHRGTX46BYBRFSKNFHG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETEJHRGTX46BYBRFSKNFHG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Using Expressions</t>
+          <t>Import Limit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,173 +671,173 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KC6S107RHDBFMTPRRNPNMY70</t>
+          <t>h_01GYETGYF8R1NB4RWM1WRRDWZ7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KC6S107RHDBFMTPRRNPNMY70</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETGYF8R1NB4RWM1WRRDWZ7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Set the Sequence of Evaluation of Rules</t>
+          <t>Source Filter Condition</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KCG27YQWM4VR8P3RPRQK74MG</t>
+          <t>h_01GYETHB98MMAZ5Q91SHB5ES0M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG27YQWM4VR8P3RPRQK74MG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETHB98MMAZ5Q91SHB5ES0M</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Import OU Rules</t>
+          <t>Create Condition</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KCG3WRW18Y2BHSHM6NM5H9M2</t>
+          <t>h_01GYETP0MHT03VXNH1DJ4HJ0QN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG3WRW18Y2BHSHM6NM5H9M2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETP0MHT03VXNH1DJ4HJ0QN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Export OU Rules</t>
+          <t>Update Condition</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KCG3WMJAJYGK7SAJGNFTYEJK</t>
+          <t>h_01GYETP5N1ENJCFYKX52KXBAYE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG3WMJAJYGK7SAJGNFTYEJK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETP5N1ENJCFYKX52KXBAYE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Refresh OU List</t>
+          <t>Map Manager</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KCG438HQYE6P3FHQGDJXWCV4</t>
+          <t>h_01GYETPGFMDGR5BSJ91HPAZBJ6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG438HQYE6P3FHQGDJXWCV4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYETPGFMDGR5BSJ91HPAZBJ6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Preview OU Assignment</t>
+          <t>Advanced Details</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KCG9WMTKZSWZ7HT2H9NDZJHB</t>
+          <t>h_01H0PWE7Q4GMR48G4DSVR28SDZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG9WMTKZSWZ7HT2H9NDZJHB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01H0PWE7Q4GMR48G4DSVR28SDZ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Termination Delay</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01JK5GN77B61SSZPDRX8YC5A52</t>
+          <t>01K56QPR4CC2535FB69KGBYMGY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JK5GN77B61SSZPDRX8YC5A52</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#01K56QPR4CC2535FB69KGBYMGY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Preview Employee Data</t>
+          <t>Allow Creation of Inactive Users</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01GBYT09A4ZDW90724KAM9MKJR</t>
+          <t>h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GBYT09A4ZDW90724KAM9MKJR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Preview Target (AD) User Attributes</t>
+          <t>Source Caching</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,107 +847,107 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01JSXWE2ZHJ1F0JCN86DE9ZMC1</t>
+          <t>h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JSXWE2ZHJ1F0JCN86DE9ZMC1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Target Caching</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+          <t>h_01K58XFVAP0BBF0GPYFKGANTV8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58XFVAP0BBF0GPYFKGANTV8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Group Management</t>
+          <t>Deactivate Users Missing in the Source Application</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01JV4TC08JCS1QTFEX02R54K3W</t>
+          <t>h_01GYEVBHHRZFZY0BG6P8MYP3G0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JV4TC08JCS1QTFEX02R54K3W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GYEVBHHRZFZY0BG6P8MYP3G0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Set Up Group Rules</t>
+          <t>Incremental Mode</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
+          <t>h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Set Up Group Retention Policy</t>
+          <t>Incremental Mode Timestamp</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+          <t>h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>On Deactivate</t>
+          <t>Phone Number Formatting</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+          <t>h_01K58CBDKGZCVACWDR6N87F3D0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58CBDKGZCVACWDR6N87F3D0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>On Update</t>
+          <t>Generate Password</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,120 +979,1616 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+          <t>h_01K56QC2SYQ3J375802JG5TNXX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56QC2SYQ3J375802JG5TNXX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Integration Execution Report in Excel Format</t>
+          <t>Password Length</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>h_01K56QC2SYQA5BQDFH815MX4AY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56QC2SYQA5BQDFH815MX4AY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Special Character Set for Password</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>h_01K56QC2SYN5ACYQ8J2BJK9QRW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56QC2SYN5ACYQ8J2BJK9QRW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Supported Functions</t>
+          <t>Report Mode</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>01K58M5YKDTY2D8NQSS0D522RH</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#01K58M5YKDTY2D8NQSS0D522RH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Limitations</t>
+          <t>Timezone Offset</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>h_01K58GZV68EVNCT3P1A0WMPJYH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58GZV68EVNCT3P1A0WMPJYH</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Skip Create and Update Failures</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K58H05A6J59JN6V0PW2WR6CP</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58H05A6J59JN6V0PW2WR6CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Update Deactivated Users</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01K56QC2SZD727X425XMAKJGKN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56QC2SZD727X425XMAKJGKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Email From Address</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>01K58M5YKE0TB613KCAN1XYP4Q</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#01K58M5YKE0TB613KCAN1XYP4Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Destination Modification Safeguard Enabled</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01K58H09SKWA8BYNHTZYK537E3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58H09SKWA8BYNHTZYK537E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Max Destination Modification Percentage</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K58H0F06C2NYWESBAA8V0ZB7</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58H0F06C2NYWESBAA8V0ZB7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>New User Integration Hook</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01K56P6WYADTWQTYGEHYQAGJPW</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56P6WYADTWQTYGEHYQAGJPW</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Update User Integration Hook</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01K56PYKTXMAQJJXJMXHFXBGVJ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56PYKTXMAQJJXJMXHFXBGVJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Deprovision User Integration Hook</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01K588CNQ6ST04AQD44J365VBY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K588CNQ6ST04AQD44J365VBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fire Hooks on Error</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01K58H00XVXSE2KPY6DHBK250F</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58H00XVXSE2KPY6DHBK250F</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Incremental Tuning</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01K58H0K9GRBQFM0TQZTHRZC1H</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58H0K9GRBQFM0TQZTHRZC1H</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Creation Notification</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KNM3SEW8R539F8VTCJENTF5D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNM3SEW8R539F8VTCJENTF5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Creation Distribution List</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KNNPJYFW2G06TYJTFP31BTSR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNPJYFW2G06TYJTFP31BTSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Creation Email Subject</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01H259NX8ZQ1SG3CV99H73XA5M</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01H259NX8ZQ1SG3CV99H73XA5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Creation Email Body</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01K56HNB40GXRHSW16X0N3EPKQ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56HNB40GXRHSW16X0N3EPKQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Send as HTML</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01K56HQ1Z0VGZ0VXWB97GS2TDK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K56HQ1Z0VGZ0VXWB97GS2TDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Send to Manager's Home Email</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01KNNPJYFXE8NJPD1MQWF175FE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNPJYFXE8NJPD1MQWF175FE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Send to Manager's Work Email</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KNNPJYFX3B4AK8YV9Y2YX7YE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNPJYFX3B4AK8YV9Y2YX7YE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Send to User's Home Email</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KNNPG18AJYYXHDA1ZGTDDZP3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNPG18AJYYXHDA1ZGTDDZP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sent to User's Work Email</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01KNNPGBR14DMN0450GVY7C89Z</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNPGBR14DMN0450GVY7C89Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Send Email To</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01KNNPHHY36W0JDRBTHTPNAPAT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNPHHY36W0JDRBTHTPNAPAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Deactivation Notification</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01K598XK6ZRCYEKPB5B55JW6FN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K598XK6ZRCYEKPB5B55JW6FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Deactivation Distribution List</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01KNNTS986S433K9T3J601DYAF</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNTS986S433K9T3J601DYAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Deactivation Email Subject</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>01K56T70CXW68YSZQRRSSCZ85K</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#01K56T70CXW68YSZQRRSSCZ85K</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Deactivation Email Body</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>01K56T70CX4XGR45WNAQQJ8HE7</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#01K56T70CX4XGR45WNAQQJ8HE7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Send as HTML</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>01K56T70CYTP83YN5KWM9QH9DM</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#01K56T70CYTP83YN5KWM9QH9DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Send to Manager's Home Email</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>h_01KNNTS987540P1W2DRNRFWY6D</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNTS987540P1W2DRNRFWY6D</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Send to Manager's Work Email</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>h_01KNNTS987JVJP0FDJ2A3D8S0F</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNTS987JVJP0FDJ2A3D8S0F</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Send Email To</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>01K56T70CY0YC9XVCK276TYHNC</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#01K56T70CY0YC9XVCK276TYHNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Admin Notification</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>h_01KNNTS987AGCSBWFBJ8ET1FQ7</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNTS987AGCSBWFBJ8ET1FQ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Admin Email List</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>h_01KNNTS987P8PDWVT3DKCTKRZ4</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNTS987P8PDWVT3DKCTKRZ4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Admin Email Subject</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>h_01KNNRJ3PJ96V9FW74G4PDNDJF</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNRJ3PJ96V9FW74G4PDNDJF</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Send Always</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>h_01KNNRS5H864B0Y8N7BYBX1X8K</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNRS5H864B0Y8N7BYBX1X8K</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Safeguard Email List</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>h_01K58XFVAQXSSG0ZYG9STYC063</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K58XFVAQXSSG0ZYG9STYC063</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Send on Report Only</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>h_01KNNRS5H9VQWPCY9BENP0QSZY</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNRS5H9VQWPCY9BENP0QSZY</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Send on Update</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>h_01KNNRS5HAM6AEBSEDC3F06XSJ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNRS5HAM6AEBSEDC3F06XSJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Send on Error</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>h_01KNNRS5HAQ8R7HRB9E02HXPFD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNRS5HAQ8R7HRB9E02HXPFD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Send on Failure</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>h_01KNNRS5HASTSD542676QNEXT0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNRS5HASTSD542676QNEXT0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Send on Safeguard Trigger</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>h_01KNNSH8YQRNRNFC5E917X7P70</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNSH8YQRNRNFC5E917X7P70</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Send Details</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>h_01KNNSH8YRBJWWJX2GHJ4BWA4T</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNSH8YRBJWWJX2GHJ4BWA4T</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Send CSV Report</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>h_01KNNSH8YRPWXR2NT4G3Y5S78W</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNSH8YRPWXR2NT4G3Y5S78W</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Send XLSX Report</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>h_01KNNSH8YRG1KG2AHGP75G8SBN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNSH8YRG1KG2AHGP75G8SBN</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Supervisions</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>h_01KNNSFQ298HGKR9CVX7W3F8GW</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNSFQ298HGKR9CVX7W3F8GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Enable Monitoring</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Mapping and Assignments</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>h_01KNNTS98737QWDK2KKS5BKB5T</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KNNTS98737QWDK2KKS5BKB5T</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>User Naming Attributes</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Preview Values of User Naming Attributes</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>h_01JTR3CGZ78E6XKPZS9QJPKP0J</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JTR3CGZ78E6XKPZS9QJPKP0J</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>OU Assignment</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Configure OU Assignment Rules</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Using Condition Builder</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Using Expressions</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>h_01KC6S107RHDBFMTPRRNPNMY70</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KC6S107RHDBFMTPRRNPNMY70</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Set the Sequence of Evaluation of Rules</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>h_01KCG27YQWM4VR8P3RPRQK74MG</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG27YQWM4VR8P3RPRQK74MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Import OU Rules</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>h_01KCG3WRW18Y2BHSHM6NM5H9M2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG3WRW18Y2BHSHM6NM5H9M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Export OU Rules</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>h_01KCG3WMJAJYGK7SAJGNFTYEJK</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG3WMJAJYGK7SAJGNFTYEJK</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Refresh OU List</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>h_01KCG438HQYE6P3FHQGDJXWCV4</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG438HQYE6P3FHQGDJXWCV4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Preview OU Assignment</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>h_01KCG9WMTKZSWZ7HT2H9NDZJHB</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KCG9WMTKZSWZ7HT2H9NDZJHB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>h_01JK5GN77B61SSZPDRX8YC5A52</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JK5GN77B61SSZPDRX8YC5A52</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Preview Employee Data</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>h_01GBYT09A4ZDW90724KAM9MKJR</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01GBYT09A4ZDW90724KAM9MKJR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Preview Target (AD) User Attributes</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>h_01JSXWE2ZHJ1F0JCN86DE9ZMC1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JSXWE2ZHJ1F0JCN86DE9ZMC1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Group Management</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>h_01JV4TC08JCS1QTFEX02R54K3W</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JV4TC08JCS1QTFEX02R54K3W</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Set Up Group Rules</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Set Up Group Retention Policy</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>On Deactivate</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>On Update</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Integration Execution Report in Excel Format</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Supported Functions</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Limitations</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>

--- a/site/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2509,7 +2509,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Integration Logs</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2519,19 +2519,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>h_01KYS4Z30XJ3ZBW70Z56D1J8QB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KYS4Z30XJ3ZBW70Z56D1J8QB</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Supported Functions</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2541,19 +2541,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>h_01KYS534CMWPVXT9JJC1SH8AZJ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01KYS534CMWPVXT9JJC1SH8AZJ</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Limitations</t>
+          <t>Appendix</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2563,32 +2563,76 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>Supported Functions</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Limitations</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Employees-to-Active-Directory-Users-V3-Integration-Guide/#h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
